--- a/Assets/LWJ/Data/TableData.xlsx
+++ b/Assets/LWJ/Data/TableData.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="630" yWindow="555" windowWidth="22335" windowHeight="8100"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="WeaponData" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="ArmorData" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="HealkitData" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="UnitBaseStatsData" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="MonsterStatsData" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="ClassStatsData" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="PerkData" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="AchievementsData" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="LevelEXPData" sheetId="9" r:id="rId12"/>
+    <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
+    <sheet name="ArmorData" sheetId="2" r:id="rId2"/>
+    <sheet name="HealkitData" sheetId="3" r:id="rId3"/>
+    <sheet name="UnitBaseStatsData" sheetId="4" r:id="rId4"/>
+    <sheet name="MonsterStatsData" sheetId="5" r:id="rId5"/>
+    <sheet name="ClassStatsData" sheetId="6" r:id="rId6"/>
+    <sheet name="PerkData" sheetId="7" r:id="rId7"/>
+    <sheet name="AchievementsData" sheetId="8" r:id="rId8"/>
+    <sheet name="LevelEXPData" sheetId="9" r:id="rId9"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
   <si>
     <t>id</t>
   </si>
@@ -54,9 +57,15 @@
     <t>weaponType</t>
   </si>
   <si>
+    <t>path</t>
+  </si>
+  <si>
     <t>rifle01</t>
   </si>
   <si>
+    <t>Assets/LWJ/Prefab/Rifle.prefab</t>
+  </si>
+  <si>
     <t>rifle02</t>
   </si>
   <si>
@@ -72,6 +81,9 @@
     <t>shotgun01</t>
   </si>
   <si>
+    <t>Assets/LWJ/Prefab/ShotGun.prefab</t>
+  </si>
+  <si>
     <t>shotgun02</t>
   </si>
   <si>
@@ -87,6 +99,9 @@
     <t>heavygun01</t>
   </si>
   <si>
+    <t>Assets/LWJ/Prefab/HeavyGun.prefab</t>
+  </si>
+  <si>
     <t>heavygun02</t>
   </si>
   <si>
@@ -102,12 +117,18 @@
     <t>revolver</t>
   </si>
   <si>
+    <t>Assets/LWJ/Prefab/Revolver.prefab</t>
+  </si>
+  <si>
     <t>knife</t>
   </si>
   <si>
     <t>melee</t>
   </si>
   <si>
+    <t>Assets/LWJ/Prefab/Knife.prefab</t>
+  </si>
+  <si>
     <t>durability</t>
   </si>
   <si>
@@ -226,22 +247,72 @@
   </si>
   <si>
     <t>nextEXP</t>
+  </si>
+  <si>
+    <t>slotType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ain</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Revolver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knife</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -250,71 +321,45 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -504,21 +549,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="13.38"/>
-    <col customWidth="1" min="5" max="5" width="13.63"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,618 +600,693 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>1001.0</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2">
         <v>0.2</v>
       </c>
       <c r="E2" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G2" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H2" s="2">
         <v>5.5</v>
       </c>
       <c r="I2" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>1002.0</v>
+        <v>1002</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D3" s="2">
         <v>0.2</v>
       </c>
       <c r="E3" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F3" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G3" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H3" s="2">
         <v>5.5</v>
       </c>
       <c r="I3" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="M3" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>1003.0</v>
+        <v>1003</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2">
         <v>0.2</v>
       </c>
       <c r="E4" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G4" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2">
         <v>5.5</v>
       </c>
       <c r="I4" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="M4" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>1004.0</v>
+        <v>1004</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2">
         <v>0.2</v>
       </c>
       <c r="E5" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G5" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H5" s="2">
         <v>5.5</v>
       </c>
       <c r="I5" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="M5" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>1005.0</v>
+        <v>1005</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2">
         <v>0.2</v>
       </c>
       <c r="E6" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G6" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2">
         <v>5.5</v>
       </c>
       <c r="I6" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="M6" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>1006.0</v>
+        <v>1006</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2">
         <v>6.5</v>
       </c>
       <c r="I7" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="L7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>1007.0</v>
+        <v>1007</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2">
         <v>6.5</v>
       </c>
       <c r="I8" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="M8" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>1008.0</v>
+        <v>1008</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H9" s="2">
         <v>6.5</v>
       </c>
       <c r="I9" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="M9" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>1009.0</v>
+        <v>1009</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G10" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2">
         <v>6.5</v>
       </c>
       <c r="I10" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="M10" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>1010.0</v>
+        <v>1010</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G11" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2">
         <v>6.5</v>
       </c>
       <c r="I11" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="M11" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>1011.0</v>
+        <v>1011</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2">
         <v>0.2</v>
       </c>
       <c r="E12" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G12" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2">
         <v>8.5</v>
       </c>
       <c r="I12" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J12" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="L12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>1012.0</v>
+        <v>1012</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2">
         <v>0.2</v>
       </c>
       <c r="E13" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F13" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G13" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H13" s="2">
         <v>8.5</v>
       </c>
       <c r="I13" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J13" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="M13" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>1013.0</v>
+        <v>1013</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <v>0.2</v>
       </c>
       <c r="E14" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F14" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G14" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H14" s="2">
         <v>8.5</v>
       </c>
       <c r="I14" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J14" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="M14" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>1014.0</v>
+        <v>1014</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2">
         <v>0.2</v>
       </c>
       <c r="E15" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F15" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G15" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H15" s="2">
         <v>8.5</v>
       </c>
       <c r="I15" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J15" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="M15" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>1015.0</v>
+        <v>1015</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2">
         <v>0.2</v>
       </c>
       <c r="E16" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F16" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G16" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2">
         <v>8.5</v>
       </c>
       <c r="I16" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="J16" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="M16" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>1016.0</v>
+        <v>1016</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D17" s="2">
         <v>0.8</v>
       </c>
       <c r="E17" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F17" s="2">
-        <v>48.0</v>
+        <v>-1</v>
       </c>
       <c r="G17" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="H17" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="L17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>1017.0</v>
+        <v>1017</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C18" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2">
         <v>0.5</v>
       </c>
       <c r="E18" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
-        <v>1.0</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H18" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="14.5"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1171,51 +1294,53 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>2001.0</v>
+        <v>2001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="D2" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2">
         <v>0.2</v>
       </c>
       <c r="F2" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1223,39 +1348,44 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>39</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>3001.0</v>
+        <v>3001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2">
-        <v>300.0</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1263,194 +1393,203 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>4001.0</v>
+        <v>4001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>5001.0</v>
+        <v>5001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>5002.0</v>
+        <v>5002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>5003.0</v>
+        <v>5003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>5004.0</v>
+        <v>5004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>4002.0</v>
+        <v>4002</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>4003.0</v>
+        <v>4003</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>4001.0</v>
+        <v>4001</v>
       </c>
       <c r="B2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>4002.0</v>
+        <v>4002</v>
       </c>
       <c r="B3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>4003.0</v>
+        <v>4003</v>
       </c>
       <c r="B4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="12.88"/>
-    <col customWidth="1" min="6" max="6" width="12.88"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1458,174 +1597,176 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>50011.0</v>
+        <v>50011</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>50012.0</v>
+        <v>50012</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>50013.0</v>
+        <v>50013</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>50014.0</v>
+        <v>50014</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>50015</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>50016</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>50017</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>50018</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>50021</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>50015.0</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>50022</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>50016.0</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>50023</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>50017.0</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>50024</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>50018.0</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>50025</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>50021.0</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>50022.0</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>50023.0</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <v>50024.0</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>50025.0</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>50026.0</v>
+        <v>50026</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>50027.0</v>
+        <v>50027</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>50028.0</v>
+        <v>50028</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1633,141 +1774,144 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>6001.0</v>
+        <v>6001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>17.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>19.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/LWJ/Data/TableData.xlsx
+++ b/Assets/LWJ/Data/TableData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="555" windowWidth="22335" windowHeight="8100"/>
+    <workbookView xWindow="630" yWindow="555" windowWidth="22335" windowHeight="8100" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
   <si>
     <t>id</t>
   </si>
@@ -275,6 +275,15 @@
   <si>
     <t>Knife</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseMainWeaponID</t>
+  </si>
+  <si>
+    <t>baseRevolverID</t>
+  </si>
+  <si>
+    <t>baseKnifeID</t>
   </si>
 </sst>
 </file>
@@ -324,7 +333,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -332,11 +341,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -344,6 +368,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1569,15 +1602,100 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>5001</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1001</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1016</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>5002</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1006</v>
+      </c>
+      <c r="D3" s="7">
+        <v>1016</v>
+      </c>
+      <c r="E3" s="7">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>5003</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1011</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1016</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>5004</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="7">
+        <v>1016</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1017</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/LWJ/Data/TableData.xlsx
+++ b/Assets/LWJ/Data/TableData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="555" windowWidth="22335" windowHeight="8100" activeTab="3"/>
+    <workbookView xWindow="630" yWindow="555" windowWidth="22335" windowHeight="8100" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
@@ -165,9 +165,6 @@
     <t>가장 기본적인 로봇이다.</t>
   </si>
   <si>
-    <t>rilfer</t>
-  </si>
-  <si>
     <t>shotguner</t>
   </si>
   <si>
@@ -284,6 +281,10 @@
   </si>
   <si>
     <t>baseKnifeID</t>
+  </si>
+  <si>
+    <t>rifler</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -637,7 +638,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -678,7 +679,7 @@
         <v>13</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -716,7 +717,7 @@
         <v>6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -754,7 +755,7 @@
         <v>6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -792,7 +793,7 @@
         <v>6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -830,7 +831,7 @@
         <v>6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -871,7 +872,7 @@
         <v>19</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -909,7 +910,7 @@
         <v>6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -947,7 +948,7 @@
         <v>6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -985,7 +986,7 @@
         <v>6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1023,7 +1024,7 @@
         <v>6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1064,7 +1065,7 @@
         <v>25</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1102,7 +1103,7 @@
         <v>6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1140,7 +1141,7 @@
         <v>6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1178,7 +1179,7 @@
         <v>6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1216,7 +1217,7 @@
         <v>6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1257,7 +1258,7 @@
         <v>31</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1298,7 +1299,7 @@
         <v>34</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1463,7 +1464,7 @@
         <v>5001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1471,7 +1472,7 @@
         <v>5002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1479,7 +1480,7 @@
         <v>5003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1487,7 +1488,7 @@
         <v>5004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1495,7 +1496,7 @@
         <v>4002</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2">
         <v>100</v>
@@ -1507,7 +1508,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -1515,7 +1516,7 @@
         <v>4003</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2">
         <v>60</v>
@@ -1527,7 +1528,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1549,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>6</v>
@@ -1617,21 +1618,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>5001</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>47</v>
+      <c r="B2" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C2" s="7">
         <v>1001</v>
@@ -1648,7 +1649,7 @@
         <v>5002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="7">
         <v>1006</v>
@@ -1665,7 +1666,7 @@
         <v>5003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="7">
         <v>1011</v>
@@ -1682,7 +1683,7 @@
         <v>5004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="7">
@@ -1723,10 +1724,10 @@
         <v>50011</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1734,10 +1735,10 @@
         <v>50012</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1745,10 +1746,10 @@
         <v>50013</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1756,10 +1757,10 @@
         <v>50014</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1767,10 +1768,10 @@
         <v>50015</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1778,10 +1779,10 @@
         <v>50016</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1789,10 +1790,10 @@
         <v>50017</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1800,10 +1801,10 @@
         <v>50018</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1811,7 +1812,7 @@
         <v>50021</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1819,7 +1820,7 @@
         <v>50022</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1827,7 +1828,7 @@
         <v>50023</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1835,7 +1836,7 @@
         <v>50024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1843,7 +1844,7 @@
         <v>50025</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1851,7 +1852,7 @@
         <v>50026</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1859,7 +1860,7 @@
         <v>50027</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -1867,7 +1868,7 @@
         <v>50028</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1900,10 +1901,10 @@
         <v>6001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1922,10 +1923,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">

--- a/Assets/LWJ/Data/TableData.xlsx
+++ b/Assets/LWJ/Data/TableData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="555" windowWidth="22335" windowHeight="8100" activeTab="5"/>
+    <workbookView xWindow="630" yWindow="555" windowWidth="22335" windowHeight="8100" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
@@ -165,9 +165,6 @@
     <t>가장 기본적인 로봇이다.</t>
   </si>
   <si>
-    <t>shotguner</t>
-  </si>
-  <si>
     <t>engineer</t>
   </si>
   <si>
@@ -274,16 +271,21 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>baseRevolverID</t>
+  </si>
+  <si>
+    <t>baseKnifeID</t>
+  </si>
+  <si>
+    <t>rifler</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>baseMainWeaponID</t>
-  </si>
-  <si>
-    <t>baseRevolverID</t>
-  </si>
-  <si>
-    <t>baseKnifeID</t>
-  </si>
-  <si>
-    <t>rifler</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shotgunner</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -638,7 +640,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -679,7 +681,7 @@
         <v>13</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -717,7 +719,7 @@
         <v>6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -755,7 +757,7 @@
         <v>6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -793,7 +795,7 @@
         <v>6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -831,7 +833,7 @@
         <v>6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -872,7 +874,7 @@
         <v>19</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -910,7 +912,7 @@
         <v>6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -948,7 +950,7 @@
         <v>6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -986,7 +988,7 @@
         <v>6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1024,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1065,7 +1067,7 @@
         <v>25</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1103,7 +1105,7 @@
         <v>6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1141,7 +1143,7 @@
         <v>6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1179,7 +1181,7 @@
         <v>6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1217,7 +1219,7 @@
         <v>6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1258,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -1299,7 +1301,7 @@
         <v>34</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1464,7 +1466,7 @@
         <v>5001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1472,7 +1474,7 @@
         <v>5002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1480,7 +1482,7 @@
         <v>5003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1488,7 +1490,7 @@
         <v>5004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1496,7 +1498,7 @@
         <v>4002</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2">
         <v>100</v>
@@ -1508,7 +1510,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -1516,7 +1518,7 @@
         <v>4003</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2">
         <v>60</v>
@@ -1528,7 +1530,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>6</v>
@@ -1606,7 +1608,8 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1618,13 +1621,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1632,7 +1635,7 @@
         <v>5001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" s="7">
         <v>1001</v>
@@ -1649,7 +1652,7 @@
         <v>5002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C3" s="7">
         <v>1006</v>
@@ -1666,7 +1669,7 @@
         <v>5003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="7">
         <v>1011</v>
@@ -1683,7 +1686,7 @@
         <v>5004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="7">
@@ -1724,10 +1727,10 @@
         <v>50011</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1735,10 +1738,10 @@
         <v>50012</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1746,10 +1749,10 @@
         <v>50013</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1757,10 +1760,10 @@
         <v>50014</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1768,10 +1771,10 @@
         <v>50015</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1779,10 +1782,10 @@
         <v>50016</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1790,10 +1793,10 @@
         <v>50017</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1801,10 +1804,10 @@
         <v>50018</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1812,7 +1815,7 @@
         <v>50021</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1820,7 +1823,7 @@
         <v>50022</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1828,7 +1831,7 @@
         <v>50023</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1836,7 +1839,7 @@
         <v>50024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1844,7 +1847,7 @@
         <v>50025</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1852,7 +1855,7 @@
         <v>50026</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1860,7 +1863,7 @@
         <v>50027</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -1868,7 +1871,7 @@
         <v>50028</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1901,10 +1904,10 @@
         <v>6001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1923,10 +1926,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
